--- a/data/vendor_map_lowes.xlsx
+++ b/data/vendor_map_lowes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\rygarcorp.com\shares\Cornerstone\Dot Com Packing Slips\1-Orders Before Extraction\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\svr01\home\gfetzer\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36B8BDF-7EB6-4F34-B1A3-14B720327922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34DA6D7B-FDCC-4C64-9568-5D48DBA2AE40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="57600" windowHeight="15555" xr2:uid="{2C04AEF6-1DD2-46BE-907B-9745C127F2C9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="77040" windowHeight="21390" xr2:uid="{2C04AEF6-1DD2-46BE-907B-9745C127F2C9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="87">
   <si>
     <t>SKU</t>
   </si>
@@ -277,6 +277,15 @@
   </si>
   <si>
     <t>Vendor</t>
+  </si>
+  <si>
+    <t>EGL1</t>
+  </si>
+  <si>
+    <t>EGLAI1</t>
+  </si>
+  <si>
+    <t>Gate Latch</t>
   </si>
 </sst>
 </file>
@@ -641,7 +650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D34B957F-2E4F-4F5D-9C8E-E382ADBC502B}">
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
@@ -939,22 +948,22 @@
       <c r="A26" t="s">
         <v>54</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>19</v>
+      <c r="B26" s="2" t="s">
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="1">
-        <v>6102</v>
+      <c r="B27" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -962,18 +971,18 @@
         <v>54</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C28" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>21</v>
+      <c r="B29" s="1">
+        <v>6102</v>
       </c>
       <c r="C29" t="s">
         <v>81</v>
@@ -984,7 +993,7 @@
         <v>54</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C30" t="s">
         <v>81</v>
@@ -995,7 +1004,7 @@
         <v>54</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C31" t="s">
         <v>81</v>
@@ -1006,7 +1015,7 @@
         <v>54</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C32" t="s">
         <v>81</v>
@@ -1017,7 +1026,7 @@
         <v>54</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C33" t="s">
         <v>81</v>
@@ -1028,29 +1037,29 @@
         <v>54</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="C34" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>54</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>26</v>
+      <c r="B35" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="C35" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>54</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>27</v>
+      <c r="B36" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="C36" t="s">
         <v>45</v>
@@ -1060,8 +1069,8 @@
       <c r="A37" t="s">
         <v>54</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>28</v>
+      <c r="B37" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="C37" t="s">
         <v>45</v>
@@ -1072,7 +1081,7 @@
         <v>54</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="C38" t="s">
         <v>45</v>
@@ -1083,7 +1092,7 @@
         <v>54</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C39" t="s">
         <v>45</v>
@@ -1094,7 +1103,7 @@
         <v>54</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="C40" t="s">
         <v>45</v>
@@ -1105,7 +1114,7 @@
         <v>54</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C41" t="s">
         <v>45</v>
@@ -1115,52 +1124,52 @@
       <c r="A42" t="s">
         <v>54</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>63</v>
+      <c r="B42" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="C42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>54</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>79</v>
+      <c r="B43" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="C43" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>54</v>
       </c>
-      <c r="B44" s="2">
-        <v>4430</v>
+      <c r="B44" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="C44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>54</v>
       </c>
-      <c r="B45" s="2">
-        <v>4442</v>
+      <c r="B45" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="C45" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>54</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>77</v>
+      <c r="B46" s="2">
+        <v>4430</v>
       </c>
       <c r="C46" t="s">
         <v>47</v>
@@ -1171,7 +1180,7 @@
         <v>54</v>
       </c>
       <c r="B47" s="2">
-        <v>4660</v>
+        <v>4442</v>
       </c>
       <c r="C47" t="s">
         <v>47</v>
@@ -1181,8 +1190,8 @@
       <c r="A48" t="s">
         <v>54</v>
       </c>
-      <c r="B48" s="2">
-        <v>6642</v>
+      <c r="B48" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="C48" t="s">
         <v>47</v>
@@ -1192,8 +1201,8 @@
       <c r="A49" t="s">
         <v>54</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>31</v>
+      <c r="B49" s="2">
+        <v>4660</v>
       </c>
       <c r="C49" t="s">
         <v>47</v>
@@ -1203,8 +1212,8 @@
       <c r="A50" t="s">
         <v>54</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>78</v>
+      <c r="B50" s="2">
+        <v>6642</v>
       </c>
       <c r="C50" t="s">
         <v>47</v>
@@ -1214,8 +1223,8 @@
       <c r="A51" t="s">
         <v>54</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>80</v>
+      <c r="B51" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="C51" t="s">
         <v>47</v>
@@ -1225,8 +1234,8 @@
       <c r="A52" t="s">
         <v>54</v>
       </c>
-      <c r="B52" s="2">
-        <v>8860</v>
+      <c r="B52" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="C52" t="s">
         <v>47</v>
@@ -1237,21 +1246,21 @@
         <v>54</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="C53" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>54</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>64</v>
+      <c r="B54" s="2">
+        <v>8860</v>
       </c>
       <c r="C54" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1259,10 +1268,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="C55" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1270,10 +1279,10 @@
         <v>54</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="C56" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1281,10 +1290,10 @@
         <v>54</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="C57" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -1292,7 +1301,7 @@
         <v>54</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C58" t="s">
         <v>74</v>
@@ -1303,7 +1312,7 @@
         <v>54</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C59" t="s">
         <v>74</v>
@@ -1314,7 +1323,7 @@
         <v>54</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C60" t="s">
         <v>74</v>
@@ -1325,7 +1334,7 @@
         <v>54</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C61" t="s">
         <v>74</v>
@@ -1336,7 +1345,7 @@
         <v>54</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C62" t="s">
         <v>74</v>
@@ -1347,7 +1356,7 @@
         <v>54</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C63" t="s">
         <v>74</v>
@@ -1358,7 +1367,7 @@
         <v>54</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C64" t="s">
         <v>74</v>
@@ -1369,10 +1378,10 @@
         <v>54</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="C65" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -1380,10 +1389,10 @@
         <v>54</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="C66" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -1391,7 +1400,7 @@
         <v>54</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C67" t="s">
         <v>75</v>
@@ -1402,7 +1411,7 @@
         <v>54</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C68" t="s">
         <v>75</v>
@@ -1413,7 +1422,7 @@
         <v>54</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C69" t="s">
         <v>75</v>
@@ -1424,7 +1433,7 @@
         <v>54</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C70" t="s">
         <v>75</v>
@@ -1435,9 +1444,31 @@
         <v>54</v>
       </c>
       <c r="B71" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C71" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>54</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C72" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>54</v>
+      </c>
+      <c r="B73" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C73" t="s">
         <v>75</v>
       </c>
     </row>
